--- a/Trading_tracker.xlsx
+++ b/Trading_tracker.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9750"/>
+    <workbookView windowWidth="18750" windowHeight="4965"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="48">
   <si>
     <t>Trade#</t>
   </si>
@@ -140,14 +140,44 @@
     <t>Wed, May 20</t>
   </si>
   <si>
+    <t>Fri, May 22</t>
+  </si>
+  <si>
     <t>Remaining Max Loss</t>
+  </si>
+  <si>
+    <t>Mon, May 25</t>
+  </si>
+  <si>
+    <t>Tues, May 26</t>
+  </si>
+  <si>
+    <t>Wed, May 27</t>
+  </si>
+  <si>
+    <t>Mon, Jun 01</t>
+  </si>
+  <si>
+    <t>Tues, Jun 02</t>
+  </si>
+  <si>
+    <t>Wed, Jun 03</t>
+  </si>
+  <si>
+    <t>Thur, Jun 04</t>
+  </si>
+  <si>
+    <t>Thur, Jun 05</t>
+  </si>
+  <si>
+    <t>Fri, Jun 05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -156,6 +186,7 @@
     <numFmt numFmtId="178" formatCode="[$-409]dddd\,mmmm\ d\,yyyy;@"/>
     <numFmt numFmtId="179" formatCode="0.00000_ "/>
     <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="&quot;US$&quot;#,##0.00;\-&quot;US$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -774,7 +805,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -790,6 +821,9 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -805,10 +839,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
@@ -1198,7 +1235,7 @@
             <c:numRef>
               <c:f>Sheet1!$L$2:$L$25</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>"US$"#,##0.00;\-"US$"#,##0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>102.52</c:v>
@@ -1229,6 +1266,42 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>642.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>617.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>719.82</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>694.82</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>795.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>770.48</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>744.93</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>855.81</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>966.15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>940.59</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1043.81</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1018.77</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1125.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1347,7 +1420,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;US$&quot;#,##0.00;\-&quot;US$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2324,11 +2397,11 @@
     <col min="4" max="4" width="13.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="15.8571428571429" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.2857142857143" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.14285714285714" style="4"/>
+    <col min="7" max="8" width="9.14285714285714" style="4"/>
     <col min="9" max="9" width="10.2857142857143" style="4" customWidth="1"/>
     <col min="10" max="10" width="10.8571428571429" customWidth="1"/>
     <col min="11" max="11" width="9.14285714285714" style="4"/>
-    <col min="12" max="12" width="16.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="16.2857142857143" style="5" customWidth="1"/>
     <col min="13" max="13" width="22.7142857142857" customWidth="1"/>
     <col min="14" max="14" width="0.142857142857143" customWidth="1"/>
     <col min="15" max="15" width="18.4285714285714" customWidth="1"/>
@@ -2339,7 +2412,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2348,28 +2421,28 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -2380,7 +2453,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
@@ -2390,7 +2463,7 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3">
@@ -2399,7 +2472,7 @@
       <c r="F2" s="3">
         <v>1.17586</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>0.44</v>
       </c>
       <c r="H2" s="4">
@@ -2414,22 +2487,22 @@
       <c r="K2" s="4">
         <v>102.52</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="5">
         <f>K2</f>
         <v>102.52</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="12" t="s">
         <v>18</v>
       </c>
       <c r="O2" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="13">
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <f t="shared" ref="A3:A13" si="0">ROW()-1</f>
         <v>2</v>
       </c>
@@ -2463,23 +2536,23 @@
       <c r="K3" s="4">
         <v>-25.2</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="5">
         <f>L2+K3</f>
         <v>77.32</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>22</v>
       </c>
       <c r="O3" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="13">
         <f>P2+SUM(K:K)</f>
-        <v>5642.95</v>
+        <v>6125.17</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2498,7 +2571,7 @@
       <c r="F4" s="3">
         <v>1.16198</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>0.38</v>
       </c>
       <c r="H4" s="4">
@@ -2513,11 +2586,11 @@
       <c r="K4" s="4">
         <v>103.36</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="5">
         <f>L3+K4</f>
         <v>180.68</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="14" t="s">
         <v>26</v>
       </c>
       <c r="O4" t="s">
@@ -2525,11 +2598,11 @@
       </c>
       <c r="P4">
         <f>COUNTA(K:K)-1</f>
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2548,7 +2621,7 @@
       <c r="F5" s="3">
         <v>1.16333</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <v>0.84</v>
       </c>
       <c r="H5" s="4">
@@ -2563,11 +2636,11 @@
       <c r="K5" s="4">
         <v>-25.2</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="5">
         <f>L4+K5</f>
         <v>155.48</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="14" t="s">
         <v>28</v>
       </c>
       <c r="O5" t="s">
@@ -2575,11 +2648,11 @@
       </c>
       <c r="P5">
         <f>COUNTIF(J:J,"Win")</f>
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2613,7 +2686,7 @@
       <c r="K6" s="4">
         <v>103.08</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="5">
         <f>L5+K6</f>
         <v>258.56</v>
       </c>
@@ -2622,11 +2695,11 @@
       </c>
       <c r="P6">
         <f>COUNTIF(J:J,"Loss")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2645,7 +2718,7 @@
       <c r="F7" s="3">
         <v>1.16387</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>0.47</v>
       </c>
       <c r="H7" s="4">
@@ -2660,20 +2733,20 @@
       <c r="K7" s="4">
         <v>-25.38</v>
       </c>
-      <c r="L7" s="10">
-        <f t="shared" ref="L5:L11" si="1">L6+K7</f>
+      <c r="L7" s="5">
+        <f t="shared" ref="L5:L22" si="1">L6+K7</f>
         <v>233.18</v>
       </c>
       <c r="O7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="15">
         <f>P5/P4</f>
-        <v>0.7</v>
+        <v>0.590909090909091</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2692,7 +2765,7 @@
       <c r="F8" s="3">
         <v>1.16441</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>1.14</v>
       </c>
       <c r="H8" s="4">
@@ -2707,19 +2780,19 @@
       <c r="K8" s="4">
         <v>101.46</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="5">
         <f t="shared" si="1"/>
         <v>334.64</v>
       </c>
       <c r="O8" t="s">
         <v>34</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="13">
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2738,7 +2811,7 @@
       <c r="F9" s="3">
         <v>1.16253</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <v>1.32</v>
       </c>
       <c r="H9" s="4">
@@ -2753,7 +2826,7 @@
       <c r="K9" s="4">
         <v>102.96</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="5">
         <f t="shared" si="1"/>
         <v>437.6</v>
       </c>
@@ -2766,7 +2839,7 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2785,7 +2858,7 @@
       <c r="F10" s="3">
         <v>1.16033</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>0.97</v>
       </c>
       <c r="H10" s="4">
@@ -2800,14 +2873,14 @@
       <c r="K10" s="4">
         <v>101.85</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="5">
         <f t="shared" si="1"/>
         <v>539.45</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="12"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2826,7 +2899,7 @@
       <c r="F11" s="3">
         <v>1.15854</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="4">
         <v>0.75</v>
       </c>
       <c r="H11" s="4">
@@ -2841,146 +2914,554 @@
       <c r="K11" s="4">
         <v>103.5</v>
       </c>
-      <c r="L11" s="10">
-        <f>L10+K11</f>
+      <c r="L11" s="5">
+        <f t="shared" si="1"/>
         <v>642.95</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.16003</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.15958</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.57</v>
+      </c>
+      <c r="H12" s="4">
+        <v>25.65</v>
+      </c>
+      <c r="I12" s="4">
+        <v>102.65</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="4">
+        <v>-25.65</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="1"/>
+        <v>617.3</v>
+      </c>
       <c r="O12" t="s">
-        <v>37</v>
-      </c>
-      <c r="P12" s="10">
+        <v>38</v>
+      </c>
+      <c r="P12" s="13">
         <f>P3-4500</f>
-        <v>1142.95</v>
+        <v>1625.17</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="8">
+    <row r="13" spans="1:12">
+      <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.16413</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.16399</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="H13" s="4">
+        <v>25.2</v>
+      </c>
+      <c r="I13" s="4">
+        <v>102.52</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="4">
+        <v>102.52</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="1"/>
+        <v>719.82</v>
+      </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="8">
+    <row r="14" spans="1:12">
+      <c r="A14" s="9">
         <f t="shared" ref="A14:A23" si="2">ROW()-1</f>
         <v>13</v>
       </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.16405</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1.1643</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>25</v>
+      </c>
+      <c r="I14" s="4">
+        <v>100</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="4">
+        <v>-25</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="1"/>
+        <v>694.82</v>
+      </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="8">
+    <row r="15" spans="1:12">
+      <c r="A15" s="9">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.16434</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.16421</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="H15" s="4">
+        <v>25.22</v>
+      </c>
+      <c r="I15" s="4">
+        <v>100.88</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100.88</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="1"/>
+        <v>795.7</v>
+      </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="8">
+    <row r="16" spans="1:12">
+      <c r="A16" s="9">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.16526</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.1647</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="H16" s="4">
+        <v>25.2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>108.36</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="4">
+        <v>-25.22</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="1"/>
+        <v>770.48</v>
+      </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="8">
+    <row r="17" spans="1:12">
+      <c r="A17" s="9">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.16101</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.16066</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="H17" s="4">
+        <v>25.55</v>
+      </c>
+      <c r="I17" s="4">
+        <v>109.86</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="4">
+        <v>-25.55</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="1"/>
+        <v>744.93</v>
+      </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="8">
+    <row r="18" spans="1:12">
+      <c r="A18" s="9">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.16371</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.16346</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4">
+        <v>25.2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>110.88</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="4">
+        <v>110.88</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="1"/>
+        <v>855.81</v>
+      </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="8">
+    <row r="19" spans="1:12">
+      <c r="A19" s="9">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.1643</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.16397</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="H19" s="4">
+        <v>26.4</v>
+      </c>
+      <c r="I19" s="4">
+        <v>110.34</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="4">
+        <v>110.34</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="1"/>
+        <v>966.15</v>
+      </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="8">
+    <row r="20" spans="1:12">
+      <c r="A20" s="9">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.16127</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1.16089</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="H20" s="4">
+        <v>25.56</v>
+      </c>
+      <c r="I20" s="4">
+        <v>102.24</v>
+      </c>
+      <c r="J20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="4">
+        <v>-25.56</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="1"/>
+        <v>940.59</v>
+      </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="8">
+    <row r="21" spans="1:12">
+      <c r="A21" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1.16018</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.15988</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="H21" s="4">
+        <v>25.8</v>
+      </c>
+      <c r="I21" s="4">
+        <v>103.22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="4">
+        <v>103.22</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="1"/>
+        <v>1043.81</v>
+      </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="8">
+    <row r="22" spans="1:12">
+      <c r="A22" s="9">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1.1625</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1.16225</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>25.04</v>
+      </c>
+      <c r="I22" s="4">
+        <v>100.8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="4">
+        <v>-25.04</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="1"/>
+        <v>1018.77</v>
+      </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="8">
+    <row r="23" spans="1:12">
+      <c r="A23" s="9">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.16138</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.16119</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="H23" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="I23" s="4">
+        <v>106.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="4">
+        <v>106.4</v>
+      </c>
+      <c r="L23" s="5">
+        <f>L22+K23</f>
+        <v>1125.17</v>
+      </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8">
+      <c r="A24" s="9">
         <f t="shared" ref="A24:A34" si="3">ROW()-1</f>
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="8">
+      <c r="A25" s="9">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8">
+      <c r="A26" s="9">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="8">
+      <c r="A27" s="9">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="8">
+      <c r="A28" s="9">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="8"/>
+      <c r="A32" s="9"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="8"/>
+      <c r="A33" s="9"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="8"/>
+      <c r="A34" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J32">
